--- a/output/male_HFD_average_of_ECG_per_age_range_kmax_10000and16000and25000_cycle_step_50_num_k_50_full.xlsx
+++ b/output/male_HFD_average_of_ECG_per_age_range_kmax_10000and16000and25000_cycle_step_50_num_k_50_full.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\HeartAge\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{27561449-88B0-4F40-A5F0-95C78E56E07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0646853A-D74E-46C7-8FC7-0A326EDFB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{7C1C472C-2926-4D29-B568-C24183C04E4D}"/>
   </bookViews>
@@ -692,7 +692,7 @@
                   </a:sysClr>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Higuchi fractal dimension (HFD) per each age range for all females</a:t>
+              <a:t>Higuchi fractal dimension (HFD) per each age range for all males</a:t>
             </a:r>
             <a:endParaRPr lang="uk-UA" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -719,16 +719,13 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="uk-UA"/>
